--- a/output/roomself_excel/10674.xlsx
+++ b/output/roomself_excel/10674.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>431330</v>
+        <v>124568</v>
       </c>
       <c r="D2" t="n">
-        <v>8540</v>
+        <v>2868</v>
       </c>
       <c r="E2" t="n">
-        <v>1178</v>
+        <v>288</v>
       </c>
       <c r="F2" t="n">
-        <v>711</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>133320</v>
+        <v>186728</v>
       </c>
       <c r="D3" t="n">
-        <v>3076</v>
+        <v>3860</v>
       </c>
       <c r="E3" t="n">
-        <v>264</v>
+        <v>475</v>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26668</v>
+        <v>133320</v>
       </c>
       <c r="D4" t="n">
-        <v>1396</v>
+        <v>3076</v>
       </c>
       <c r="E4" t="n">
-        <v>113</v>
+        <v>264</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19890</v>
+        <v>116688</v>
       </c>
       <c r="D5" t="n">
-        <v>1148</v>
+        <v>2824</v>
       </c>
       <c r="E5" t="n">
-        <v>117</v>
+        <v>264</v>
       </c>
       <c r="F5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>116688</v>
+        <v>89701</v>
       </c>
       <c r="D6" t="n">
-        <v>2824</v>
+        <v>2408</v>
       </c>
       <c r="E6" t="n">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>89701</v>
+        <v>120034</v>
       </c>
       <c r="D8" t="n">
-        <v>2408</v>
+        <v>3192</v>
       </c>
       <c r="E8" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -630,10 +630,10 @@
         <v>1384</v>
       </c>
       <c r="E9" t="n">
-        <v>428</v>
+        <v>202</v>
       </c>
       <c r="F9" t="n">
-        <v>187</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26293</v>
+        <v>26668</v>
       </c>
       <c r="D10" t="n">
-        <v>1300</v>
+        <v>1396</v>
       </c>
       <c r="E10" t="n">
-        <v>217</v>
+        <v>113</v>
       </c>
       <c r="F10" t="n">
-        <v>154</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -678,6 +678,50 @@
       </c>
       <c r="F11" t="n">
         <v>218</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>19890</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1148</v>
+      </c>
+      <c r="E12" t="n">
+        <v>117</v>
+      </c>
+      <c r="F12" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>26293</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E13" t="n">
+        <v>217</v>
+      </c>
+      <c r="F13" t="n">
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/10674.xlsx
+++ b/output/roomself_excel/10674.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>2868</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>288</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>22</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +525,27 @@
       <c r="D3" t="n">
         <v>3860</v>
       </c>
-      <c r="E3" t="n">
-        <v>475</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>423</v>
+        <v>375</v>
+      </c>
+      <c r="G3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>603</v>
+      </c>
+      <c r="J3" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +563,27 @@
       <c r="D4" t="n">
         <v>3076</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>264</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>22</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>505</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -541,10 +601,26 @@
       <c r="D5" t="n">
         <v>2824</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>442</v>
+      </c>
+      <c r="G5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>264</v>
       </c>
-      <c r="F5" t="n">
+      <c r="J5" t="n">
         <v>21</v>
       </c>
     </row>
@@ -563,11 +639,27 @@
       <c r="D6" t="n">
         <v>2408</v>
       </c>
-      <c r="E6" t="n">
-        <v>292</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>114</v>
+        <v>93</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>271</v>
+      </c>
+      <c r="J6" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +677,20 @@
       <c r="D7" t="n">
         <v>1668</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>247</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>24</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +707,12 @@
       <c r="D8" t="n">
         <v>3192</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +729,20 @@
       <c r="D9" t="n">
         <v>1384</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>202</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>21</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +759,20 @@
       <c r="D10" t="n">
         <v>1396</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>113</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>24</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,11 +789,27 @@
       <c r="D11" t="n">
         <v>1964</v>
       </c>
-      <c r="E11" t="n">
-        <v>299</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>218</v>
+        <v>598</v>
+      </c>
+      <c r="G11" t="n">
+        <v>13</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>192</v>
+      </c>
+      <c r="J11" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -695,12 +827,20 @@
       <c r="D12" t="n">
         <v>1148</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>117</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>24</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,11 +857,27 @@
       <c r="D13" t="n">
         <v>1300</v>
       </c>
-      <c r="E13" t="n">
-        <v>217</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F13" t="n">
         <v>154</v>
+      </c>
+      <c r="G13" t="n">
+        <v>24</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>93</v>
+      </c>
+      <c r="J13" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
